--- a/CYP2B6/CYP2B6_frequency_table.xlsx
+++ b/CYP2B6/CYP2B6_frequency_table.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP2B6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ctoma\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP2B6\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Allele frequency" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="2207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4370" uniqueCount="2202">
   <si>
     <t>CYP2B6 allele</t>
   </si>
@@ -5310,9 +5310,6 @@
     <t>0.11734093</t>
   </si>
   <si>
-    <t>0.05357082</t>
-  </si>
-  <si>
     <t>0.1231214</t>
   </si>
   <si>
@@ -5331,9 +5328,6 @@
     <t>0.0436291</t>
   </si>
   <si>
-    <t>0.07428478</t>
-  </si>
-  <si>
     <t>0.09452413</t>
   </si>
   <si>
@@ -5358,9 +5352,6 @@
     <t>0.48562673</t>
   </si>
   <si>
-    <t>0.42950228</t>
-  </si>
-  <si>
     <t>0.33582056</t>
   </si>
   <si>
@@ -5385,9 +5376,6 @@
     <t>0.32628936</t>
   </si>
   <si>
-    <t>0.37952113</t>
-  </si>
-  <si>
     <t>0.42165288</t>
   </si>
   <si>
@@ -5410,9 +5398,6 @@
   </si>
   <si>
     <t>0.020025712</t>
-  </si>
-  <si>
-    <t>0.06145065</t>
   </si>
   <si>
     <t>0.013596146</t>
@@ -6676,7 +6661,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6686,6 +6671,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -6725,7 +6716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -6766,6 +6757,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17310,7 +17308,7 @@
     <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -17343,7 +17341,7 @@
       <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="9" t="s">
@@ -17372,8 +17370,8 @@
       <c r="D3" s="6" t="s">
         <v>1259</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>1260</v>
+      <c r="E3" s="17">
+        <v>1.6704408999999999E-3</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>1261</v>
@@ -17401,14 +17399,14 @@
       <c r="D4" s="6" t="s">
         <v>1759</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="17">
+        <v>5.3570819999999998E-2</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>1760</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>1761</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>1762</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>23</v>
@@ -17419,118 +17417,118 @@
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>1763</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>1764</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>1765</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="17">
+        <v>7.4284779999999995E-2</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>1766</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>1767</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>1768</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>1769</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>1770</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>1772</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>1773</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="17">
+        <v>0.42950228000000001</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>1774</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>1775</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>1776</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>1777</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>1778</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>1779</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>1781</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="E7" s="17">
+        <v>0.37952112999999998</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>1782</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>1783</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>1784</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>1785</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>1786</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>1787</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>1788</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>1789</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E8" s="17">
+        <v>6.1450650000000002E-2</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>1790</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="G8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>1791</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>1793</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>1794</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>1795</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>1796</v>
       </c>
     </row>
   </sheetData>
@@ -17580,28 +17578,28 @@
   <sheetData>
     <row r="1" spans="1:46" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>1797</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>1798</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>1799</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>1800</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>1801</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>1802</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>1803</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>1804</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>9</v>
@@ -17631,7 +17629,7 @@
         <v>54</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>1805</v>
+        <v>1800</v>
       </c>
       <c r="S1" s="9" t="s">
         <v>61</v>
@@ -17640,7 +17638,7 @@
         <v>66</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="V1" s="9" t="s">
         <v>68</v>
@@ -17670,13 +17668,13 @@
         <v>88</v>
       </c>
       <c r="AE1" s="9" t="s">
-        <v>1807</v>
+        <v>1802</v>
       </c>
       <c r="AF1" s="9" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="AG1" s="9" t="s">
-        <v>1809</v>
+        <v>1804</v>
       </c>
       <c r="AH1" s="9" t="s">
         <v>91</v>
@@ -17685,10 +17683,10 @@
         <v>93</v>
       </c>
       <c r="AJ1" s="9" t="s">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="AK1" s="9" t="s">
-        <v>1811</v>
+        <v>1806</v>
       </c>
       <c r="AL1" s="9" t="s">
         <v>94</v>
@@ -17697,22 +17695,22 @@
         <v>95</v>
       </c>
       <c r="AN1" s="9" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AO1" s="9" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AP1" s="9" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AQ1" s="9" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AR1" s="9" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AS1" s="9" t="s">
         <v>1812</v>
-      </c>
-      <c r="AO1" s="9" t="s">
-        <v>1813</v>
-      </c>
-      <c r="AP1" s="9" t="s">
-        <v>1814</v>
-      </c>
-      <c r="AQ1" s="9" t="s">
-        <v>1815</v>
-      </c>
-      <c r="AR1" s="9" t="s">
-        <v>1816</v>
-      </c>
-      <c r="AS1" s="9" t="s">
-        <v>1817</v>
       </c>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
@@ -17720,154 +17718,154 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="T2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="U2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="X2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Y2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Z2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AA2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AB2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AC2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AD2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AE2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AF2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AG2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AH2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AI2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AJ2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AK2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AL2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AM2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AN2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AO2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AP2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AQ2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AR2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AS2" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AT2" s="14"/>
     </row>
     <row r="3" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B3" s="5">
         <v>2005</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1821</v>
+        <v>1816</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -17875,10 +17873,10 @@
         <v>70</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1822</v>
+        <v>1817</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1823</v>
+        <v>1818</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>23</v>
@@ -17887,10 +17885,10 @@
         <v>23</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1824</v>
+        <v>1819</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1825</v>
+        <v>1820</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>23</v>
@@ -17905,7 +17903,7 @@
         <v>76</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>23</v>
@@ -17922,49 +17920,49 @@
     </row>
     <row r="4" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="B4" s="5">
         <v>2010</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1828</v>
+        <v>1823</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1830</v>
+        <v>1825</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="5">
         <v>282</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1831</v>
+        <v>1826</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>1832</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="5" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1833</v>
+        <v>1828</v>
       </c>
       <c r="B5" s="5">
         <v>2011</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1834</v>
+        <v>1829</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -17972,57 +17970,57 @@
         <v>27</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1836</v>
+        <v>1831</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1838</v>
+        <v>1833</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1839</v>
+        <v>1834</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B6" s="5">
         <v>2012</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1821</v>
+        <v>1816</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H6" s="5">
         <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>23</v>
@@ -18030,61 +18028,61 @@
     </row>
     <row r="7" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B7" s="5">
         <v>2012</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1845</v>
+        <v>1840</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H7" s="5">
         <v>24</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1846</v>
+        <v>1841</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1847</v>
+        <v>1842</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>1848</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1821</v>
+        <v>1816</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1849</v>
+        <v>1844</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="H8" s="5">
         <v>61</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1851</v>
+        <v>1846</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>50</v>
@@ -18107,38 +18105,38 @@
     </row>
     <row r="9" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H9" s="10" t="s">
+        <v>1848</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>1850</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>1852</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>1853</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="L9" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="M9" s="11" t="s">
         <v>1855</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="N9" s="11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="11" t="s">
         <v>1857</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>1858</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>1859</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>1860</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>1861</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q9" s="11" t="s">
-        <v>1862</v>
       </c>
       <c r="R9" s="11"/>
       <c r="S9" s="11" t="s">
-        <v>1863</v>
+        <v>1858</v>
       </c>
       <c r="T9" s="11" t="s">
         <v>23</v>
@@ -18154,7 +18152,7 @@
         <v>76</v>
       </c>
       <c r="Y9" s="11" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
       <c r="Z9" s="11" t="s">
         <v>23</v>
@@ -18189,69 +18187,69 @@
     </row>
     <row r="10" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H10" s="10" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>1822</v>
+        <v>1817</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>1838</v>
+        <v>1833</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="R10" s="11"/>
       <c r="S10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U10" s="11"/>
       <c r="V10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="X10" s="11" t="s">
         <v>76</v>
       </c>
       <c r="Y10" s="11" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AA10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AB10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC10" s="11" t="s">
         <v>37</v>
       </c>
       <c r="AD10" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE10" s="11"/>
       <c r="AF10" s="11"/>
@@ -18271,69 +18269,69 @@
     </row>
     <row r="11" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H11" s="10" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>1823</v>
+        <v>1818</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>50</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>1824</v>
+        <v>1819</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>1847</v>
+        <v>1842</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Q11" s="11" t="s">
-        <v>1839</v>
+        <v>1834</v>
       </c>
       <c r="R11" s="11"/>
       <c r="S11" s="11" t="s">
-        <v>1832</v>
+        <v>1827</v>
       </c>
       <c r="T11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U11" s="11"/>
       <c r="V11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="X11" s="11" t="s">
         <v>76</v>
       </c>
       <c r="Y11" s="11" t="s">
-        <v>1848</v>
+        <v>1843</v>
       </c>
       <c r="Z11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AA11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AB11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC11" s="11" t="s">
         <v>37</v>
       </c>
       <c r="AD11" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE11" s="11"/>
       <c r="AF11" s="11"/>
@@ -18356,154 +18354,154 @@
         <v>2</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="P13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="S13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="T13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="U13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="V13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="W13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="X13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Y13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Z13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AA13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AB13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AD13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AE13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AF13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AG13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AH13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AI13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AJ13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AK13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AL13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AM13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AN13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AO13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AP13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AQ13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AR13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AS13" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AT13" s="14"/>
     </row>
     <row r="14" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
       <c r="B14" s="5">
         <v>2012</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1866</v>
+        <v>1861</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1867</v>
+        <v>1862</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -18511,7 +18509,7 @@
         <v>63</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1868</v>
+        <v>1863</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>19</v>
@@ -18531,31 +18529,31 @@
     </row>
     <row r="15" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B15" s="5">
         <v>2015</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1871</v>
+        <v>1866</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1872</v>
+        <v>1867</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H15" s="5">
         <v>86</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1873</v>
+        <v>1868</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>23</v>
@@ -18578,31 +18576,31 @@
     </row>
     <row r="16" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B16" s="5">
         <v>2015</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1874</v>
+        <v>1869</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1875</v>
+        <v>1870</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H16" s="5">
         <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>23</v>
@@ -18620,39 +18618,39 @@
         <v>23</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="17" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B17" s="5">
         <v>2015</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1878</v>
+        <v>1873</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H17" s="5">
         <v>102</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>23</v>
@@ -18672,31 +18670,31 @@
     </row>
     <row r="18" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B18" s="5">
         <v>2015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1881</v>
+        <v>1876</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H18" s="5">
         <v>96</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>23</v>
@@ -18719,34 +18717,34 @@
     </row>
     <row r="19" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B19" s="5">
         <v>2015</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1883</v>
+        <v>1878</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H19" s="5">
         <v>102</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>23</v>
@@ -18766,41 +18764,41 @@
     </row>
     <row r="20" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>1887</v>
+        <v>1882</v>
       </c>
       <c r="H20" s="5">
         <v>11485</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1888</v>
+        <v>1883</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>1891</v>
+        <v>1886</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>1892</v>
+        <v>1887</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>23</v>
@@ -18817,16 +18815,16 @@
     </row>
     <row r="21" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H21" s="10" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>1893</v>
+        <v>1888</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>1894</v>
+        <v>1889</v>
       </c>
       <c r="L21" s="11" t="s">
         <v>31</v>
@@ -18842,17 +18840,17 @@
       </c>
       <c r="R21" s="11"/>
       <c r="S21" s="11" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="T21" s="11" t="s">
         <v>23</v>
       </c>
       <c r="U21" s="11"/>
       <c r="V21" s="11" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
@@ -18863,7 +18861,7 @@
       </c>
       <c r="AC21" s="11"/>
       <c r="AD21" s="11" t="s">
-        <v>1900</v>
+        <v>1895</v>
       </c>
       <c r="AE21" s="11"/>
       <c r="AF21" s="11"/>
@@ -18889,16 +18887,16 @@
     </row>
     <row r="22" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H22" s="10" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>1868</v>
+        <v>1863</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L22" s="11" t="s">
         <v>31</v>
@@ -18914,43 +18912,43 @@
       </c>
       <c r="R22" s="11"/>
       <c r="S22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
       <c r="Z22" s="11"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC22" s="11"/>
       <c r="AD22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE22" s="11"/>
       <c r="AF22" s="11"/>
       <c r="AG22" s="11"/>
       <c r="AH22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AI22" s="11"/>
       <c r="AJ22" s="11"/>
       <c r="AK22" s="11"/>
       <c r="AL22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AM22" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AN22" s="11"/>
       <c r="AO22" s="11"/>
@@ -18961,16 +18959,16 @@
     </row>
     <row r="23" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H23" s="10" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="L23" s="11" t="s">
         <v>31</v>
@@ -18989,40 +18987,40 @@
         <v>92</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U23" s="11"/>
       <c r="V23" s="11" t="s">
-        <v>1897</v>
+        <v>1892</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
       <c r="Z23" s="11"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC23" s="11"/>
       <c r="AD23" s="11" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="AE23" s="11"/>
       <c r="AF23" s="11"/>
       <c r="AG23" s="11"/>
       <c r="AH23" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="11"/>
       <c r="AK23" s="11"/>
       <c r="AL23" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AM23" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AN23" s="11"/>
       <c r="AO23" s="11"/>
@@ -19036,154 +19034,154 @@
         <v>3</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="P25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Q25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="R25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="S25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="T25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="U25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="V25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="W25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="X25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Y25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Z25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AA25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AB25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AC25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AE25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AF25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AG25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AH25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AI25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AJ25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AK25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AL25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AM25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AN25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AO25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AP25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AQ25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AR25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AS25" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AT25" s="14"/>
     </row>
     <row r="26" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>1901</v>
+        <v>1896</v>
       </c>
       <c r="B26" s="5">
         <v>2002</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -19191,22 +19189,22 @@
         <v>530</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1907</v>
+        <v>1902</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>23</v>
@@ -19214,19 +19212,19 @@
     </row>
     <row r="27" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B27" s="5">
         <v>2005</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -19234,19 +19232,19 @@
         <v>50</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1908</v>
+        <v>1903</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1848</v>
+        <v>1843</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>1909</v>
+        <v>1904</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>23</v>
@@ -19272,19 +19270,19 @@
     </row>
     <row r="28" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B28" s="5">
         <v>2005</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -19292,10 +19290,10 @@
         <v>90</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1912</v>
+        <v>1907</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>23</v>
@@ -19306,19 +19304,19 @@
     </row>
     <row r="29" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B29" s="5">
         <v>2005</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -19326,19 +19324,19 @@
         <v>88</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1915</v>
+        <v>1910</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1916</v>
+        <v>1911</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1917</v>
+        <v>1912</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>23</v>
@@ -19364,19 +19362,19 @@
     </row>
     <row r="30" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B30" s="5">
         <v>2005</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -19384,10 +19382,10 @@
         <v>96</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1918</v>
+        <v>1913</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>23</v>
@@ -19398,19 +19396,19 @@
     </row>
     <row r="31" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B31" s="5">
         <v>2005</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -19418,19 +19416,19 @@
         <v>68</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1921</v>
+        <v>1916</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1924</v>
+        <v>1919</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>23</v>
@@ -19456,19 +19454,19 @@
     </row>
     <row r="32" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B32" s="5">
         <v>2005</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -19476,10 +19474,10 @@
         <v>92</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1925</v>
+        <v>1920</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>23</v>
@@ -19490,19 +19488,19 @@
     </row>
     <row r="33" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
       <c r="B33" s="5">
         <v>2006</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -19510,51 +19508,51 @@
         <v>386</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1932</v>
+        <v>1927</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="34" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B34" s="5">
         <v>2012</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H34" s="5">
         <v>25</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="Y34" s="2" t="s">
         <v>23</v>
@@ -19562,34 +19560,34 @@
     </row>
     <row r="35" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B35" s="5">
         <v>2012</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H35" s="5">
         <v>68</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1938</v>
+        <v>1933</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1939</v>
+        <v>1934</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>23</v>
@@ -19597,34 +19595,34 @@
     </row>
     <row r="36" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B36" s="5">
         <v>2012</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1940</v>
+        <v>1935</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H36" s="5">
         <v>84</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
       <c r="Y36" s="2" t="s">
         <v>23</v>
@@ -19632,19 +19630,19 @@
     </row>
     <row r="37" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
       <c r="B37" s="5">
         <v>2012</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1866</v>
+        <v>1861</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -19652,16 +19650,16 @@
         <v>165</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>1944</v>
+        <v>1939</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1946</v>
+        <v>1941</v>
       </c>
       <c r="Q37" s="2" t="s">
         <v>60</v>
@@ -19669,19 +19667,19 @@
     </row>
     <row r="38" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
       <c r="B38" s="5">
         <v>2012</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1866</v>
+        <v>1861</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1947</v>
+        <v>1942</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -19689,19 +19687,19 @@
         <v>196</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1893</v>
+        <v>1888</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>50</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1948</v>
+        <v>1943</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>50</v>
@@ -19709,31 +19707,31 @@
     </row>
     <row r="39" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B39" s="5">
         <v>2015</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1951</v>
+        <v>1946</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H39" s="5">
         <v>93</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>23</v>
@@ -19756,31 +19754,31 @@
     </row>
     <row r="40" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B40" s="5">
         <v>2015</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1953</v>
+        <v>1948</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H40" s="5">
         <v>103</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>23</v>
@@ -19803,31 +19801,31 @@
     </row>
     <row r="41" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B41" s="5">
         <v>2015</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1955</v>
+        <v>1950</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1956</v>
+        <v>1951</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H41" s="5">
         <v>104</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>23</v>
@@ -19850,31 +19848,31 @@
     </row>
     <row r="42" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B42" s="5">
         <v>2015</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1958</v>
+        <v>1953</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>1959</v>
+        <v>1954</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H42" s="5">
         <v>99</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>23</v>
@@ -19897,31 +19895,31 @@
     </row>
     <row r="43" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B43" s="5">
         <v>2015</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1960</v>
+        <v>1955</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H43" s="5">
         <v>105</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>23</v>
@@ -19944,32 +19942,32 @@
     </row>
     <row r="44" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H44" s="10" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>1962</v>
+        <v>1957</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>1964</v>
+        <v>1959</v>
       </c>
       <c r="M44" s="11" t="s">
         <v>37</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>1965</v>
+        <v>1960</v>
       </c>
       <c r="O44" s="11" t="s">
         <v>23</v>
       </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11" t="s">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="R44" s="11"/>
       <c r="S44" s="11" t="s">
@@ -20002,7 +20000,7 @@
       </c>
       <c r="AC44" s="11"/>
       <c r="AD44" s="11" t="s">
-        <v>1967</v>
+        <v>1962</v>
       </c>
       <c r="AE44" s="11"/>
       <c r="AF44" s="11"/>
@@ -20024,65 +20022,65 @@
     </row>
     <row r="45" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H45" s="10" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>1921</v>
+        <v>1916</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>50</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>1916</v>
+        <v>1911</v>
       </c>
       <c r="M45" s="11" t="s">
         <v>37</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="O45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="R45" s="11"/>
       <c r="S45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="T45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U45" s="11"/>
       <c r="V45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="X45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Y45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Z45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AA45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AB45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC45" s="11"/>
       <c r="AD45" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE45" s="11"/>
       <c r="AF45" s="11"/>
@@ -20104,28 +20102,28 @@
     </row>
     <row r="46" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H46" s="10" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="M46" s="11" t="s">
         <v>37</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="O46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="11" t="s">
@@ -20133,32 +20131,32 @@
       </c>
       <c r="R46" s="11"/>
       <c r="S46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="T46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="X46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Y46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Z46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AA46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AB46" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC46" s="11"/>
       <c r="AD46" s="11" t="s">
@@ -20187,154 +20185,154 @@
         <v>4</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="M48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="N48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="P48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Q48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="R48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="S48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="T48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="U48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="V48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="W48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="X48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Y48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Z48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AA48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AB48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AC48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AD48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AE48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AF48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AG48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AH48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AI48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AJ48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AK48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AL48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AM48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AN48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AO48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AP48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AQ48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AR48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AS48" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AT48" s="14"/>
     </row>
     <row r="49" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>1968</v>
+        <v>1963</v>
       </c>
       <c r="B49" s="5">
         <v>2001</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -20342,64 +20340,64 @@
         <v>215</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>1848</v>
+        <v>1843</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1973</v>
+        <v>1968</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="50" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>1975</v>
+        <v>1970</v>
       </c>
       <c r="B50" s="5">
         <v>2004</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1976</v>
+        <v>1971</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>1977</v>
+        <v>1972</v>
       </c>
       <c r="H50" s="5">
         <v>135</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1978</v>
+        <v>1973</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>1979</v>
+        <v>1974</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>23</v>
@@ -20407,19 +20405,19 @@
     </row>
     <row r="51" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1981</v>
+        <v>1976</v>
       </c>
       <c r="B51" s="5">
         <v>2004</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1982</v>
+        <v>1977</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -20427,16 +20425,16 @@
         <v>255</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1983</v>
+        <v>1978</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
       <c r="V51" s="2" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>51</v>
@@ -20444,19 +20442,19 @@
     </row>
     <row r="52" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B52" s="5">
         <v>2005</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -20464,64 +20462,64 @@
         <v>430</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1985</v>
+        <v>1980</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>1986</v>
+        <v>1981</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1973</v>
+        <v>1968</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="53" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="B53" s="5">
         <v>2007</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1988</v>
+        <v>1983</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1989</v>
+        <v>1984</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
       <c r="H53" s="5">
         <v>141</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1991</v>
+        <v>1986</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>1993</v>
+        <v>1988</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="X53" s="2" t="s">
         <v>23</v>
@@ -20541,19 +20539,19 @@
     </row>
     <row r="54" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="B54" s="5">
         <v>2010</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1998</v>
+        <v>1993</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -20561,16 +20559,16 @@
         <v>180</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="Q54" s="2" t="s">
         <v>58</v>
@@ -20578,64 +20576,64 @@
     </row>
     <row r="55" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="B55" s="5">
         <v>2010</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1828</v>
+        <v>1823</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>1830</v>
+        <v>1825</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="5">
         <v>399</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="56" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B56" s="5">
         <v>2012</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H56" s="5">
         <v>43</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="Y56" s="2" t="s">
         <v>23</v>
@@ -20643,31 +20641,31 @@
     </row>
     <row r="57" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B57" s="5">
         <v>2012</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H57" s="5">
         <v>59</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>23</v>
@@ -20675,34 +20673,34 @@
     </row>
     <row r="58" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B58" s="5">
         <v>2012</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H58" s="5">
         <v>36</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="Y58" s="2" t="s">
         <v>23</v>
@@ -20710,34 +20708,34 @@
     </row>
     <row r="59" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B59" s="5">
         <v>2012</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H59" s="5">
         <v>90</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
       <c r="Y59" s="2" t="s">
         <v>23</v>
@@ -20745,34 +20743,34 @@
     </row>
     <row r="60" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B60" s="5">
         <v>2012</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H60" s="5">
         <v>92</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>23</v>
@@ -20780,37 +20778,37 @@
     </row>
     <row r="61" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B61" s="5">
         <v>2015</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H61" s="5">
         <v>91</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>23</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="T61" s="2" t="s">
         <v>23</v>
@@ -20819,7 +20817,7 @@
         <v>23</v>
       </c>
       <c r="W61" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="AD61" s="2" t="s">
         <v>23</v>
@@ -20827,31 +20825,31 @@
     </row>
     <row r="62" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B62" s="5">
         <v>2015</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H62" s="5">
         <v>99</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>23</v>
@@ -20874,37 +20872,37 @@
     </row>
     <row r="63" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B63" s="5">
         <v>2015</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H63" s="5">
         <v>107</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>23</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="T63" s="2" t="s">
         <v>23</v>
@@ -20913,7 +20911,7 @@
         <v>23</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="AD63" s="2" t="s">
         <v>23</v>
@@ -20921,34 +20919,34 @@
     </row>
     <row r="64" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B64" s="5">
         <v>2015</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H64" s="5">
         <v>107</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>23</v>
@@ -20968,37 +20966,37 @@
     </row>
     <row r="65" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B65" s="5">
         <v>2015</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H65" s="5">
         <v>99</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1983</v>
+        <v>1978</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>23</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="T65" s="2" t="s">
         <v>23</v>
@@ -21007,7 +21005,7 @@
         <v>23</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="AD65" s="2" t="s">
         <v>23</v>
@@ -21015,16 +21013,16 @@
     </row>
     <row r="66" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -21032,22 +21030,22 @@
         <v>11138</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="T66" s="2" t="s">
         <v>23</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="AB66" s="2" t="s">
         <v>23</v>
@@ -21064,16 +21062,16 @@
     </row>
     <row r="67" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -21081,31 +21079,31 @@
         <v>55856</v>
       </c>
       <c r="I67" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="W67" s="2" t="s">
         <v>2033</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="AB67" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD67" s="2" t="s">
         <v>2034</v>
       </c>
-      <c r="S67" s="2" t="s">
+      <c r="AL67" s="2" t="s">
         <v>2035</v>
-      </c>
-      <c r="T67" s="2" t="s">
-        <v>2036</v>
-      </c>
-      <c r="V67" s="2" t="s">
-        <v>2037</v>
-      </c>
-      <c r="W67" s="2" t="s">
-        <v>2038</v>
-      </c>
-      <c r="AB67" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD67" s="2" t="s">
-        <v>2039</v>
-      </c>
-      <c r="AL67" s="2" t="s">
-        <v>2040</v>
       </c>
       <c r="AM67" s="2" t="s">
         <v>23</v>
@@ -21113,28 +21111,28 @@
     </row>
     <row r="68" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H68" s="10" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="I68" s="11" t="s">
+        <v>2037</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>2038</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>2039</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>2040</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>2041</v>
+      </c>
+      <c r="N68" s="11" t="s">
         <v>2042</v>
       </c>
-      <c r="J68" s="11" t="s">
-        <v>2043</v>
-      </c>
-      <c r="K68" s="11" t="s">
+      <c r="O68" s="11" t="s">
         <v>2044</v>
-      </c>
-      <c r="L68" s="11" t="s">
-        <v>2045</v>
-      </c>
-      <c r="M68" s="11" t="s">
-        <v>2046</v>
-      </c>
-      <c r="N68" s="11" t="s">
-        <v>2047</v>
-      </c>
-      <c r="O68" s="11" t="s">
-        <v>2049</v>
       </c>
       <c r="P68" s="11"/>
       <c r="Q68" s="11" t="s">
@@ -21142,17 +21140,17 @@
       </c>
       <c r="R68" s="11"/>
       <c r="S68" s="11" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="T68" s="11" t="s">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="U68" s="11"/>
       <c r="V68" s="11" t="s">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="W68" s="11" t="s">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="X68" s="11" t="s">
         <v>23</v>
@@ -21169,7 +21167,7 @@
         <v>87</v>
       </c>
       <c r="AD68" s="11" t="s">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="AE68" s="11"/>
       <c r="AF68" s="11"/>
@@ -21183,7 +21181,7 @@
       <c r="AJ68" s="11"/>
       <c r="AK68" s="11"/>
       <c r="AL68" s="11" t="s">
-        <v>2056</v>
+        <v>2051</v>
       </c>
       <c r="AM68" s="11" t="s">
         <v>23</v>
@@ -21197,28 +21195,28 @@
     </row>
     <row r="69" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H69" s="10" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L69" s="11" t="s">
-        <v>1979</v>
+        <v>1974</v>
       </c>
       <c r="M69" s="11" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="N69" s="11" t="s">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="O69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="P69" s="11"/>
       <c r="Q69" s="11" t="s">
@@ -21226,51 +21224,51 @@
       </c>
       <c r="R69" s="11"/>
       <c r="S69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="T69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U69" s="11"/>
       <c r="V69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="X69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Y69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Z69" s="11"/>
       <c r="AA69" s="11"/>
       <c r="AB69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC69" s="11" t="s">
         <v>87</v>
       </c>
       <c r="AD69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE69" s="11"/>
       <c r="AF69" s="11"/>
       <c r="AG69" s="11"/>
       <c r="AH69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AI69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AJ69" s="11"/>
       <c r="AK69" s="11"/>
       <c r="AL69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AM69" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AN69" s="11"/>
       <c r="AO69" s="11"/>
@@ -21281,28 +21279,28 @@
     </row>
     <row r="70" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H70" s="10" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>1986</v>
+        <v>1981</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="L70" s="11" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="M70" s="11" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="N70" s="11" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="O70" s="11" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="P70" s="11"/>
       <c r="Q70" s="11" t="s">
@@ -21310,51 +21308,51 @@
       </c>
       <c r="R70" s="11"/>
       <c r="S70" s="11" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="T70" s="11" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
       <c r="U70" s="11"/>
       <c r="V70" s="11" t="s">
         <v>51</v>
       </c>
       <c r="W70" s="11" t="s">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="X70" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Y70" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Z70" s="11"/>
       <c r="AA70" s="11"/>
       <c r="AB70" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC70" s="11" t="s">
         <v>87</v>
       </c>
       <c r="AD70" s="11" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="AE70" s="11"/>
       <c r="AF70" s="11"/>
       <c r="AG70" s="11"/>
       <c r="AH70" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AI70" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AJ70" s="11"/>
       <c r="AK70" s="11"/>
       <c r="AL70" s="11" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="AM70" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AN70" s="11"/>
       <c r="AO70" s="11"/>
@@ -21368,173 +21366,173 @@
         <v>5</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="I72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="L72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="M72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="N72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="P72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Q72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="R72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="S72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="T72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="U72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="V72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="W72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="X72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Y72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Z72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AA72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AB72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AC72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AD72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AE72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AF72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AG72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AH72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AI72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AJ72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AK72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AL72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AM72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AN72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AO72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AP72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AQ72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AR72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AS72" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AT72" s="14"/>
     </row>
     <row r="73" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="B73" s="5">
         <v>2007</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1988</v>
+        <v>1983</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
       <c r="H73" s="5">
         <v>7</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>76</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>23</v>
@@ -21557,19 +21555,19 @@
     </row>
     <row r="74" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="B74" s="5">
         <v>2010</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>2062</v>
+        <v>2057</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -21577,46 +21575,46 @@
         <v>181</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>2066</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="75" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="B75" s="5">
         <v>2010</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1828</v>
+        <v>1823</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>2067</v>
+        <v>2062</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>1830</v>
+        <v>1825</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="5">
         <v>150</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="S75" s="2" t="s">
         <v>23</v>
@@ -21624,19 +21622,19 @@
     </row>
     <row r="76" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>1833</v>
+        <v>1828</v>
       </c>
       <c r="B76" s="5">
         <v>2011</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1834</v>
+        <v>1829</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>2068</v>
+        <v>2063</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -21644,25 +21642,25 @@
         <v>125</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>21</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="Y76" s="2" t="s">
         <v>52</v>
@@ -21670,34 +21668,34 @@
     </row>
     <row r="77" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B77" s="5">
         <v>2012</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H77" s="5">
         <v>17</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="Y77" s="2" t="s">
         <v>23</v>
@@ -21705,66 +21703,66 @@
     </row>
     <row r="78" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B78" s="5">
         <v>2012</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>2076</v>
+        <v>2071</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H78" s="5">
         <v>5</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>2077</v>
+        <v>2072</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="Y78" s="2" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="79" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H79" s="5">
         <v>94</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>23</v>
@@ -21776,7 +21774,7 @@
         <v>23</v>
       </c>
       <c r="V79" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="W79" s="2" t="s">
         <v>23</v>
@@ -21787,31 +21785,31 @@
     </row>
     <row r="80" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B80" s="5">
         <v>2015</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>2082</v>
+        <v>2077</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>2083</v>
+        <v>2078</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H80" s="5">
         <v>64</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>23</v>
@@ -21834,31 +21832,31 @@
     </row>
     <row r="81" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>2084</v>
+        <v>2079</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>2085</v>
+        <v>2080</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H81" s="5">
         <v>85</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>23</v>
@@ -21867,7 +21865,7 @@
         <v>23</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="V81" s="2" t="s">
         <v>51</v>
@@ -21881,31 +21879,31 @@
     </row>
     <row r="82" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B82" s="5">
         <v>2015</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>2088</v>
+        <v>2083</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H82" s="5">
         <v>104</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>23</v>
@@ -21928,7 +21926,7 @@
     </row>
     <row r="83" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
@@ -21939,28 +21937,28 @@
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2" t="s">
-        <v>1887</v>
+        <v>1882</v>
       </c>
       <c r="H83" s="5">
         <v>13686</v>
       </c>
       <c r="I83" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="S83" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="T83" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="W83" s="2" t="s">
         <v>2089</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>2090</v>
-      </c>
-      <c r="S83" s="2" t="s">
-        <v>2091</v>
-      </c>
-      <c r="T83" s="2" t="s">
-        <v>2092</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>2093</v>
-      </c>
-      <c r="W83" s="2" t="s">
-        <v>2094</v>
       </c>
       <c r="AB83" s="2" t="s">
         <v>23</v>
@@ -21977,52 +21975,52 @@
     </row>
     <row r="84" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H84" s="10" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>21</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>2098</v>
+        <v>2093</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>2099</v>
+        <v>2094</v>
       </c>
       <c r="N84" s="11" t="s">
-        <v>2100</v>
+        <v>2095</v>
       </c>
       <c r="O84" s="11" t="s">
         <v>50</v>
       </c>
       <c r="P84" s="11"/>
       <c r="Q84" s="11" t="s">
-        <v>2101</v>
+        <v>2096</v>
       </c>
       <c r="R84" s="11"/>
       <c r="S84" s="11" t="s">
-        <v>2102</v>
+        <v>2097</v>
       </c>
       <c r="T84" s="11" t="s">
-        <v>2104</v>
+        <v>2099</v>
       </c>
       <c r="U84" s="11"/>
       <c r="V84" s="11" t="s">
-        <v>2102</v>
+        <v>2097</v>
       </c>
       <c r="W84" s="11" t="s">
-        <v>2105</v>
+        <v>2100</v>
       </c>
       <c r="X84" s="11" t="s">
         <v>23</v>
       </c>
       <c r="Y84" s="11" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="Z84" s="11"/>
       <c r="AA84" s="11"/>
@@ -22048,7 +22046,7 @@
         <v>23</v>
       </c>
       <c r="AM84" s="11" t="s">
-        <v>2107</v>
+        <v>2102</v>
       </c>
       <c r="AN84" s="11"/>
       <c r="AO84" s="11"/>
@@ -22059,78 +22057,78 @@
     </row>
     <row r="85" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H85" s="10" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
       <c r="J85" s="11" t="s">
         <v>21</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="N85" s="11" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="O85" s="11" t="s">
         <v>50</v>
       </c>
       <c r="P85" s="11"/>
       <c r="Q85" s="11" t="s">
-        <v>2066</v>
+        <v>2061</v>
       </c>
       <c r="R85" s="11"/>
       <c r="S85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="T85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U85" s="11"/>
       <c r="V85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="X85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Y85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Z85" s="11"/>
       <c r="AA85" s="11"/>
       <c r="AB85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC85" s="11"/>
       <c r="AD85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE85" s="11"/>
       <c r="AF85" s="11"/>
       <c r="AG85" s="11"/>
       <c r="AH85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AI85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AJ85" s="11"/>
       <c r="AK85" s="11"/>
       <c r="AL85" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AM85" s="11" t="s">
-        <v>2107</v>
+        <v>2102</v>
       </c>
       <c r="AN85" s="11"/>
       <c r="AO85" s="11"/>
@@ -22141,39 +22139,39 @@
     </row>
     <row r="86" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H86" s="10" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>21</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>2097</v>
+        <v>2092</v>
       </c>
       <c r="L86" s="11" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
       <c r="M86" s="11" t="s">
         <v>76</v>
       </c>
       <c r="N86" s="11" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="O86" s="11" t="s">
         <v>50</v>
       </c>
       <c r="P86" s="11"/>
       <c r="Q86" s="11" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="R86" s="11"/>
       <c r="S86" s="11" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="T86" s="11" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="U86" s="11"/>
       <c r="V86" s="11" t="s">
@@ -22183,36 +22181,36 @@
         <v>87</v>
       </c>
       <c r="X86" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Y86" s="11" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
       <c r="Z86" s="11"/>
       <c r="AA86" s="11"/>
       <c r="AB86" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AC86" s="11"/>
       <c r="AD86" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE86" s="11"/>
       <c r="AF86" s="11"/>
       <c r="AG86" s="11"/>
       <c r="AH86" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AI86" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AJ86" s="11"/>
       <c r="AK86" s="11"/>
       <c r="AL86" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AM86" s="11" t="s">
-        <v>2107</v>
+        <v>2102</v>
       </c>
       <c r="AN86" s="11"/>
       <c r="AO86" s="11"/>
@@ -22226,160 +22224,160 @@
         <v>6</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="I88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="L88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="M88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="N88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="P88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Q88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="R88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="S88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="T88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="U88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="V88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="W88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="X88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Y88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Z88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AA88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AB88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AC88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AD88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AE88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AF88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AG88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AH88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AI88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AJ88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AK88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AL88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AM88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AN88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AO88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AP88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AQ88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AR88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AS88" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AT88" s="14"/>
     </row>
     <row r="89" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
       <c r="B89" s="5">
         <v>2014</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>2109</v>
+        <v>2104</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>2111</v>
+        <v>2106</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="H89" s="5">
         <v>206</v>
@@ -22408,7 +22406,7 @@
     </row>
     <row r="90" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H90" s="10" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>14</v>
@@ -22464,7 +22462,7 @@
     </row>
     <row r="91" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H91" s="10" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I91" s="11" t="s">
         <v>14</v>
@@ -22520,7 +22518,7 @@
     </row>
     <row r="92" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H92" s="10" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>14</v>
@@ -22579,154 +22577,154 @@
         <v>7</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="G94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="I94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="K94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="L94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="M94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="N94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="P94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Q94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="R94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="S94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="T94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="U94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="V94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="W94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="X94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Y94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Z94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AA94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AB94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AC94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AD94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AE94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AF94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AG94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AH94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AI94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AJ94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AK94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AL94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AM94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AN94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AO94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AP94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AQ94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AR94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AS94" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AT94" s="14"/>
     </row>
     <row r="95" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>2113</v>
+        <v>2108</v>
       </c>
       <c r="B95" s="5">
         <v>2006</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -22734,7 +22732,7 @@
         <v>174</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>23</v>
@@ -22760,10 +22758,10 @@
     </row>
     <row r="96" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H96" s="10" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>2117</v>
+        <v>2112</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>23</v>
@@ -22818,19 +22816,19 @@
     </row>
     <row r="97" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H97" s="10" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
       <c r="J97" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="K97" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L97" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="M97" s="11" t="s">
         <v>40</v>
@@ -22876,19 +22874,19 @@
     </row>
     <row r="98" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H98" s="10" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
       <c r="J98" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L98" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="M98" s="11" t="s">
         <v>40</v>
@@ -22937,164 +22935,164 @@
         <v>8</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="H100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="I100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="K100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="L100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="M100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="N100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="P100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Q100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="R100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="S100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="T100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="U100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="V100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="W100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="X100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Y100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="Z100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AA100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AB100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AC100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AD100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AE100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AF100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AG100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AH100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AI100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AJ100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AK100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AL100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AM100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AN100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AO100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AP100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AQ100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AR100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AS100" s="15" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="AT100" s="14"/>
     </row>
     <row r="101" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B101" s="5">
         <v>2005</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2" t="s">
-        <v>2119</v>
+        <v>2114</v>
       </c>
       <c r="H101" s="5">
         <v>82</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>23</v>
@@ -23102,19 +23100,19 @@
     </row>
     <row r="102" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B102" s="5">
         <v>2005</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -23122,7 +23120,7 @@
         <v>64</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>24</v>
@@ -23134,7 +23132,7 @@
         <v>23</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="O102" s="2" t="s">
         <v>52</v>
@@ -23157,35 +23155,35 @@
     </row>
     <row r="103" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="B103" s="5">
         <v>2007</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1988</v>
+        <v>1983</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>2122</v>
+        <v>2117</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
       <c r="H103" s="5">
         <v>16</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>2123</v>
+        <v>2118</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>23</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>2124</v>
+        <v>2119</v>
       </c>
       <c r="S103" s="2" t="s">
         <v>23</v>
@@ -23194,10 +23192,10 @@
         <v>23</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>2125</v>
+        <v>2120</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="AC103" s="2" t="s">
         <v>24</v>
@@ -23211,35 +23209,35 @@
     </row>
     <row r="104" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
       <c r="B104" s="5">
         <v>2009</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>2129</v>
+        <v>2124</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2" t="s">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="H104" s="5">
         <v>121</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
       <c r="AB104" s="2" t="s">
         <v>37</v>
@@ -23247,270 +23245,270 @@
     </row>
     <row r="105" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B105" s="5">
         <v>2012</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>2134</v>
+        <v>2129</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H105" s="5">
         <v>67</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>2135</v>
+        <v>2130</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>2136</v>
+        <v>2131</v>
       </c>
       <c r="Y105" s="2" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="106" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="B106" s="5">
         <v>2012</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>2137</v>
+        <v>2132</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="H106" s="5">
         <v>78</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>2138</v>
+        <v>2133</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>2139</v>
+        <v>2134</v>
       </c>
       <c r="Y106" s="2" t="s">
-        <v>2140</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="107" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>2141</v>
+        <v>2136</v>
       </c>
       <c r="B107" s="5">
         <v>2012</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>2142</v>
+        <v>2137</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>2143</v>
+        <v>2138</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>2144</v>
+        <v>2139</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="5">
         <v>49</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="Y107" s="2" t="s">
-        <v>1936</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="108" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>2147</v>
+        <v>2142</v>
       </c>
       <c r="B108" s="5">
         <v>2013</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>2148</v>
+        <v>2143</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>2150</v>
+        <v>2145</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>2151</v>
+        <v>2146</v>
       </c>
       <c r="H108" s="5">
         <v>163</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>2152</v>
+        <v>2147</v>
       </c>
       <c r="M108" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>2153</v>
+        <v>2148</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>2154</v>
+        <v>2149</v>
       </c>
       <c r="Y108" s="2" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="109" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>2147</v>
+        <v>2142</v>
       </c>
       <c r="B109" s="5">
         <v>2013</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>2148</v>
+        <v>2143</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>2150</v>
+        <v>2145</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
       <c r="H109" s="5">
         <v>295</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>2156</v>
+        <v>2151</v>
       </c>
       <c r="S109" s="2" t="s">
-        <v>2157</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="110" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
       <c r="B110" s="5">
         <v>2014</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2" t="s">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="H110" s="5">
         <v>106</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>2161</v>
+        <v>2156</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>2162</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="111" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
       <c r="B111" s="5">
         <v>2014</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2" t="s">
-        <v>2163</v>
+        <v>2158</v>
       </c>
       <c r="H111" s="5">
         <v>157</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="112" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B112" s="5">
         <v>2015</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>2166</v>
+        <v>2161</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H112" s="5">
         <v>99</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>23</v>
@@ -23533,31 +23531,31 @@
     </row>
     <row r="113" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B113" s="5">
         <v>2015</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H113" s="5">
         <v>113</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>23</v>
@@ -23580,37 +23578,37 @@
     </row>
     <row r="114" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B114" s="5">
         <v>2015</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>2170</v>
+        <v>2165</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>2171</v>
+        <v>2166</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H114" s="5">
         <v>99</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>23</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="T114" s="2" t="s">
         <v>23</v>
@@ -23627,31 +23625,31 @@
     </row>
     <row r="115" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B115" s="5">
         <v>2015</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>2173</v>
+        <v>2168</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H115" s="5">
         <v>85</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>23</v>
@@ -23674,31 +23672,31 @@
     </row>
     <row r="116" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B116" s="5">
         <v>2015</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H116" s="5">
         <v>108</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>23</v>
@@ -23721,40 +23719,40 @@
     </row>
     <row r="117" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
       <c r="B117" s="5">
         <v>2016</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2" t="s">
-        <v>2178</v>
+        <v>2173</v>
       </c>
       <c r="H117" s="5">
         <v>158</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H118" s="10" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>2179</v>
+        <v>2174</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>24</v>
@@ -23769,7 +23767,7 @@
         <v>40</v>
       </c>
       <c r="N118" s="11" t="s">
-        <v>2124</v>
+        <v>2119</v>
       </c>
       <c r="O118" s="11" t="s">
         <v>52</v>
@@ -23778,7 +23776,7 @@
       <c r="Q118" s="11"/>
       <c r="R118" s="11"/>
       <c r="S118" s="11" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="T118" s="11" t="s">
         <v>23</v>
@@ -23788,13 +23786,13 @@
         <v>23</v>
       </c>
       <c r="W118" s="11" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
       <c r="X118" s="11" t="s">
         <v>77</v>
       </c>
       <c r="Y118" s="11" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="Z118" s="11" t="s">
         <v>52</v>
@@ -23803,7 +23801,7 @@
         <v>52</v>
       </c>
       <c r="AB118" s="11" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="AC118" s="11" t="s">
         <v>24</v>
@@ -23833,25 +23831,25 @@
     </row>
     <row r="119" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H119" s="10" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I119" s="11" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
       <c r="J119" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K119" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L119" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="M119" s="11" t="s">
         <v>40</v>
       </c>
       <c r="N119" s="11" t="s">
-        <v>2139</v>
+        <v>2134</v>
       </c>
       <c r="O119" s="11" t="s">
         <v>52</v>
@@ -23860,23 +23858,23 @@
       <c r="Q119" s="11"/>
       <c r="R119" s="11"/>
       <c r="S119" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="T119" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U119" s="11"/>
       <c r="V119" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W119" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="X119" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="Y119" s="11" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="Z119" s="11" t="s">
         <v>52</v>
@@ -23891,7 +23889,7 @@
         <v>24</v>
       </c>
       <c r="AD119" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE119" s="11"/>
       <c r="AF119" s="11"/>
@@ -23915,25 +23913,25 @@
     </row>
     <row r="120" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H120" s="10" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K120" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L120" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="M120" s="11" t="s">
         <v>40</v>
       </c>
       <c r="N120" s="11" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="O120" s="11" t="s">
         <v>52</v>
@@ -23942,23 +23940,23 @@
       <c r="Q120" s="11"/>
       <c r="R120" s="11"/>
       <c r="S120" s="11" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="T120" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="U120" s="11"/>
       <c r="V120" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="W120" s="11" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
       <c r="X120" s="11" t="s">
-        <v>2125</v>
+        <v>2120</v>
       </c>
       <c r="Y120" s="11" t="s">
-        <v>2140</v>
+        <v>2135</v>
       </c>
       <c r="Z120" s="11" t="s">
         <v>52</v>
@@ -23973,7 +23971,7 @@
         <v>24</v>
       </c>
       <c r="AD120" s="11" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="AE120" s="11"/>
       <c r="AF120" s="11"/>
@@ -24020,77 +24018,77 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>2189</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="126" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="126" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>2191</v>
+        <v>2186</v>
       </c>
     </row>
   </sheetData>
@@ -24108,32 +24106,32 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>2193</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>2194</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="4" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>2195</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>2196</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
     </row>
   </sheetData>
@@ -24152,10 +24150,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -24163,7 +24161,7 @@
         <v>44631</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2200</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -24171,7 +24169,7 @@
         <v>43920</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2201</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -24179,7 +24177,7 @@
         <v>43889</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -24187,7 +24185,7 @@
         <v>43760</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -24195,7 +24193,7 @@
         <v>43453</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -24203,7 +24201,7 @@
         <v>43284</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2205</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -24211,7 +24209,7 @@
         <v>43264</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
     </row>
   </sheetData>
